--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216548</v>
+        <v>121216556</v>
       </c>
       <c r="B12" t="n">
-        <v>90705</v>
+        <v>94093</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>2383</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511619</v>
+        <v>511617</v>
       </c>
       <c r="R12" t="n">
-        <v>6733592</v>
+        <v>6733638</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216556</v>
+        <v>121216548</v>
       </c>
       <c r="B13" t="n">
-        <v>94093</v>
+        <v>90705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2383</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511617</v>
+        <v>511619</v>
       </c>
       <c r="R13" t="n">
-        <v>6733638</v>
+        <v>6733592</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216537</v>
+        <v>121216497</v>
       </c>
       <c r="B7" t="n">
-        <v>97025</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511618</v>
+        <v>511620</v>
       </c>
       <c r="R7" t="n">
-        <v>6733644</v>
+        <v>6733607</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216561</v>
+        <v>121216498</v>
       </c>
       <c r="B8" t="n">
-        <v>100337</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511610</v>
+        <v>511626</v>
       </c>
       <c r="R8" t="n">
-        <v>6733625</v>
+        <v>6733600</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216497</v>
+        <v>121216560</v>
       </c>
       <c r="B9" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,25 +1469,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511620</v>
+        <v>511618</v>
       </c>
       <c r="R9" t="n">
-        <v>6733607</v>
+        <v>6733644</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216554</v>
+        <v>121216556</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>94103</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2383</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511638</v>
+        <v>511617</v>
       </c>
       <c r="R10" t="n">
-        <v>6733637</v>
+        <v>6733638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216498</v>
+        <v>121216554</v>
       </c>
       <c r="B11" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,21 +1677,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511626</v>
+        <v>511638</v>
       </c>
       <c r="R11" t="n">
-        <v>6733600</v>
+        <v>6733637</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216556</v>
+        <v>121216561</v>
       </c>
       <c r="B12" t="n">
-        <v>94093</v>
+        <v>100347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2383</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511617</v>
+        <v>511610</v>
       </c>
       <c r="R12" t="n">
-        <v>6733638</v>
+        <v>6733625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216548</v>
+        <v>121216537</v>
       </c>
       <c r="B13" t="n">
-        <v>90705</v>
+        <v>97035</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511619</v>
+        <v>511618</v>
       </c>
       <c r="R13" t="n">
-        <v>6733592</v>
+        <v>6733644</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216560</v>
+        <v>121216548</v>
       </c>
       <c r="B14" t="n">
-        <v>100337</v>
+        <v>90715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511618</v>
+        <v>511619</v>
       </c>
       <c r="R14" t="n">
-        <v>6733644</v>
+        <v>6733592</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216497</v>
+        <v>121216554</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511620</v>
+        <v>511638</v>
       </c>
       <c r="R7" t="n">
-        <v>6733607</v>
+        <v>6733637</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216498</v>
+        <v>121216561</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511626</v>
+        <v>511610</v>
       </c>
       <c r="R8" t="n">
-        <v>6733600</v>
+        <v>6733625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216554</v>
+        <v>121216498</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,21 +1677,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511638</v>
+        <v>511626</v>
       </c>
       <c r="R11" t="n">
-        <v>6733637</v>
+        <v>6733600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216561</v>
+        <v>121216548</v>
       </c>
       <c r="B12" t="n">
-        <v>100347</v>
+        <v>90715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511610</v>
+        <v>511619</v>
       </c>
       <c r="R12" t="n">
-        <v>6733625</v>
+        <v>6733592</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216548</v>
+        <v>121216497</v>
       </c>
       <c r="B14" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511619</v>
+        <v>511620</v>
       </c>
       <c r="R14" t="n">
-        <v>6733592</v>
+        <v>6733607</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216554</v>
+        <v>121216561</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>100347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511638</v>
+        <v>511610</v>
       </c>
       <c r="R7" t="n">
-        <v>6733637</v>
+        <v>6733625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216561</v>
+        <v>121216554</v>
       </c>
       <c r="B8" t="n">
-        <v>100347</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511610</v>
+        <v>511638</v>
       </c>
       <c r="R8" t="n">
-        <v>6733625</v>
+        <v>6733637</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2067,6 +2067,340 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121467155</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91149</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>511671</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6733613</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121467157</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90674</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>511654</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6733619</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121467146</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>511614</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6733603</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216561</v>
+        <v>121216548</v>
       </c>
       <c r="B7" t="n">
-        <v>100347</v>
+        <v>90727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511610</v>
+        <v>511619</v>
       </c>
       <c r="R7" t="n">
-        <v>6733625</v>
+        <v>6733592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216554</v>
+        <v>121216560</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>100360</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511638</v>
+        <v>511618</v>
       </c>
       <c r="R8" t="n">
-        <v>6733637</v>
+        <v>6733644</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216560</v>
+        <v>121216561</v>
       </c>
       <c r="B9" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511618</v>
+        <v>511610</v>
       </c>
       <c r="R9" t="n">
-        <v>6733644</v>
+        <v>6733625</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216556</v>
+        <v>121216537</v>
       </c>
       <c r="B10" t="n">
-        <v>94103</v>
+        <v>97048</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2383</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511617</v>
+        <v>511618</v>
       </c>
       <c r="R10" t="n">
-        <v>6733638</v>
+        <v>6733644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
         <v>121216498</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216548</v>
+        <v>121216556</v>
       </c>
       <c r="B12" t="n">
-        <v>90715</v>
+        <v>94115</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>2383</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511619</v>
+        <v>511617</v>
       </c>
       <c r="R12" t="n">
-        <v>6733592</v>
+        <v>6733638</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216537</v>
+        <v>121216554</v>
       </c>
       <c r="B13" t="n">
-        <v>97035</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511618</v>
+        <v>511638</v>
       </c>
       <c r="R13" t="n">
-        <v>6733644</v>
+        <v>6733637</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1970,7 @@
         <v>121216497</v>
       </c>
       <c r="B14" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467155</v>
+        <v>121467146</v>
       </c>
       <c r="B15" t="n">
-        <v>91149</v>
+        <v>90709</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,41 +2081,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511671</v>
+        <v>511614</v>
       </c>
       <c r="R15" t="n">
-        <v>6733613</v>
+        <v>6733603</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2145,28 +2142,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2185,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467157</v>
+        <v>121467155</v>
       </c>
       <c r="B16" t="n">
-        <v>90674</v>
+        <v>91149</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,25 +2183,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511654</v>
+        <v>511671</v>
       </c>
       <c r="R16" t="n">
-        <v>6733619</v>
+        <v>6733613</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2263,7 +2249,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2259,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467146</v>
+        <v>121467157</v>
       </c>
       <c r="B17" t="n">
-        <v>90709</v>
+        <v>90674</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,38 +2299,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511614</v>
+        <v>511654</v>
       </c>
       <c r="R17" t="n">
-        <v>6733603</v>
+        <v>6733619</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2374,17 +2363,28 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216548</v>
+        <v>121216537</v>
       </c>
       <c r="B7" t="n">
-        <v>90727</v>
+        <v>97049</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511619</v>
+        <v>511618</v>
       </c>
       <c r="R7" t="n">
-        <v>6733592</v>
+        <v>6733644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216560</v>
+        <v>121216556</v>
       </c>
       <c r="B8" t="n">
-        <v>100360</v>
+        <v>94116</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>2383</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511618</v>
+        <v>511617</v>
       </c>
       <c r="R8" t="n">
-        <v>6733644</v>
+        <v>6733638</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
         <v>121216561</v>
       </c>
       <c r="B9" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216537</v>
+        <v>121216554</v>
       </c>
       <c r="B10" t="n">
-        <v>97048</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511618</v>
+        <v>511638</v>
       </c>
       <c r="R10" t="n">
-        <v>6733644</v>
+        <v>6733637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
         <v>121216498</v>
       </c>
       <c r="B11" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216556</v>
+        <v>121216497</v>
       </c>
       <c r="B12" t="n">
-        <v>94115</v>
+        <v>90710</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2383</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511617</v>
+        <v>511620</v>
       </c>
       <c r="R12" t="n">
-        <v>6733638</v>
+        <v>6733607</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216554</v>
+        <v>121216560</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>100361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511638</v>
+        <v>511618</v>
       </c>
       <c r="R13" t="n">
-        <v>6733637</v>
+        <v>6733644</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216497</v>
+        <v>121216548</v>
       </c>
       <c r="B14" t="n">
-        <v>90709</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511620</v>
+        <v>511619</v>
       </c>
       <c r="R14" t="n">
-        <v>6733607</v>
+        <v>6733592</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467146</v>
+        <v>121467155</v>
       </c>
       <c r="B15" t="n">
-        <v>90709</v>
+        <v>91150</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,38 +2081,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511614</v>
+        <v>511671</v>
       </c>
       <c r="R15" t="n">
-        <v>6733603</v>
+        <v>6733613</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2142,17 +2145,28 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2171,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467155</v>
+        <v>121467146</v>
       </c>
       <c r="B16" t="n">
-        <v>91149</v>
+        <v>90710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,41 +2197,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511671</v>
+        <v>511614</v>
       </c>
       <c r="R16" t="n">
-        <v>6733613</v>
+        <v>6733603</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2247,28 +2258,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>121467157</v>
       </c>
       <c r="B17" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216537</v>
+        <v>121216554</v>
       </c>
       <c r="B7" t="n">
-        <v>97049</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511618</v>
+        <v>511638</v>
       </c>
       <c r="R7" t="n">
-        <v>6733644</v>
+        <v>6733637</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216556</v>
+        <v>121216537</v>
       </c>
       <c r="B8" t="n">
-        <v>94116</v>
+        <v>97052</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2383</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511617</v>
+        <v>511618</v>
       </c>
       <c r="R8" t="n">
-        <v>6733638</v>
+        <v>6733644</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216561</v>
+        <v>121216560</v>
       </c>
       <c r="B9" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511610</v>
+        <v>511618</v>
       </c>
       <c r="R9" t="n">
-        <v>6733625</v>
+        <v>6733644</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216554</v>
+        <v>121216561</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>100364</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511638</v>
+        <v>511610</v>
       </c>
       <c r="R10" t="n">
-        <v>6733637</v>
+        <v>6733625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216498</v>
+        <v>121216497</v>
       </c>
       <c r="B11" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511626</v>
+        <v>511620</v>
       </c>
       <c r="R11" t="n">
-        <v>6733600</v>
+        <v>6733607</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216497</v>
+        <v>121216498</v>
       </c>
       <c r="B12" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511620</v>
+        <v>511626</v>
       </c>
       <c r="R12" t="n">
-        <v>6733607</v>
+        <v>6733600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216560</v>
+        <v>121216548</v>
       </c>
       <c r="B13" t="n">
-        <v>100361</v>
+        <v>90731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511618</v>
+        <v>511619</v>
       </c>
       <c r="R13" t="n">
-        <v>6733644</v>
+        <v>6733592</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216548</v>
+        <v>121216556</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>94119</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>2383</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511619</v>
+        <v>511617</v>
       </c>
       <c r="R14" t="n">
-        <v>6733592</v>
+        <v>6733638</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467155</v>
+        <v>121467146</v>
       </c>
       <c r="B15" t="n">
-        <v>91150</v>
+        <v>90713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,41 +2081,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511671</v>
+        <v>511614</v>
       </c>
       <c r="R15" t="n">
-        <v>6733613</v>
+        <v>6733603</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2145,28 +2142,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2185,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467146</v>
+        <v>121467157</v>
       </c>
       <c r="B16" t="n">
-        <v>90710</v>
+        <v>90678</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,38 +2183,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511614</v>
+        <v>511654</v>
       </c>
       <c r="R16" t="n">
-        <v>6733603</v>
+        <v>6733619</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,17 +2247,28 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467157</v>
+        <v>121467155</v>
       </c>
       <c r="B17" t="n">
-        <v>90675</v>
+        <v>91153</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,25 +2299,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511654</v>
+        <v>511671</v>
       </c>
       <c r="R17" t="n">
-        <v>6733619</v>
+        <v>6733613</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,6 +2400,116 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121515491</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56566</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>511409</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6733523</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216554</v>
+        <v>121216556</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>94119</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2383</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511638</v>
+        <v>511617</v>
       </c>
       <c r="R7" t="n">
-        <v>6733637</v>
+        <v>6733638</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216537</v>
+        <v>121216497</v>
       </c>
       <c r="B8" t="n">
-        <v>97052</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511618</v>
+        <v>511620</v>
       </c>
       <c r="R8" t="n">
-        <v>6733644</v>
+        <v>6733607</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216560</v>
+        <v>121216554</v>
       </c>
       <c r="B9" t="n">
-        <v>100364</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,25 +1469,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511618</v>
+        <v>511638</v>
       </c>
       <c r="R9" t="n">
-        <v>6733644</v>
+        <v>6733637</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216561</v>
+        <v>121216498</v>
       </c>
       <c r="B10" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511610</v>
+        <v>511626</v>
       </c>
       <c r="R10" t="n">
-        <v>6733625</v>
+        <v>6733600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216497</v>
+        <v>121216560</v>
       </c>
       <c r="B11" t="n">
-        <v>90713</v>
+        <v>100364</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,25 +1673,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511620</v>
+        <v>511618</v>
       </c>
       <c r="R11" t="n">
-        <v>6733607</v>
+        <v>6733644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216498</v>
+        <v>121216537</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>97052</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511626</v>
+        <v>511618</v>
       </c>
       <c r="R12" t="n">
-        <v>6733600</v>
+        <v>6733644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216548</v>
+        <v>121216561</v>
       </c>
       <c r="B13" t="n">
-        <v>90731</v>
+        <v>100364</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511619</v>
+        <v>511610</v>
       </c>
       <c r="R13" t="n">
-        <v>6733592</v>
+        <v>6733625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216556</v>
+        <v>121216548</v>
       </c>
       <c r="B14" t="n">
-        <v>94119</v>
+        <v>90731</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2383</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511617</v>
+        <v>511619</v>
       </c>
       <c r="R14" t="n">
-        <v>6733638</v>
+        <v>6733592</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467157</v>
+        <v>121533633</v>
       </c>
       <c r="B16" t="n">
-        <v>90678</v>
+        <v>90727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,25 +2183,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2210,17 +2210,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511654</v>
+        <v>511457</v>
       </c>
       <c r="R16" t="n">
-        <v>6733619</v>
+        <v>6733528</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,6 +2378,11 @@
           <t>13:37</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Jättegranlåga</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2403,7 +2408,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515491</v>
+        <v>121535165</v>
       </c>
       <c r="B18" t="n">
         <v>56566</v>
@@ -2441,17 +2446,17 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511409</v>
+        <v>511406</v>
       </c>
       <c r="R18" t="n">
         <v>6733523</v>
@@ -2484,9 +2489,24 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2510,6 +2530,619 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121515491</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56566</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>511409</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6733523</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121467157</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90678</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>511654</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6733619</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121529050</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stor Moberg Norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>511468</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6733517</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121534290</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stor Moberg , Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>511631</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6733617</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121520970</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90678</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stor Moberg Norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>511488</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6733530</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216556</v>
+        <v>121216537</v>
       </c>
       <c r="B7" t="n">
-        <v>94119</v>
+        <v>97058</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2383</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511617</v>
+        <v>511618</v>
       </c>
       <c r="R7" t="n">
-        <v>6733638</v>
+        <v>6733644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216497</v>
+        <v>121216560</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511620</v>
+        <v>511618</v>
       </c>
       <c r="R8" t="n">
-        <v>6733607</v>
+        <v>6733644</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216554</v>
+        <v>121216548</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511638</v>
+        <v>511619</v>
       </c>
       <c r="R9" t="n">
-        <v>6733637</v>
+        <v>6733592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
         <v>121216498</v>
       </c>
       <c r="B10" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216560</v>
+        <v>121216556</v>
       </c>
       <c r="B11" t="n">
-        <v>100364</v>
+        <v>94125</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,21 +1677,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2383</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511618</v>
+        <v>511617</v>
       </c>
       <c r="R11" t="n">
-        <v>6733644</v>
+        <v>6733638</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216537</v>
+        <v>121216561</v>
       </c>
       <c r="B12" t="n">
-        <v>97052</v>
+        <v>100370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511618</v>
+        <v>511610</v>
       </c>
       <c r="R12" t="n">
-        <v>6733644</v>
+        <v>6733625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216561</v>
+        <v>121216497</v>
       </c>
       <c r="B13" t="n">
-        <v>100364</v>
+        <v>90719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511610</v>
+        <v>511620</v>
       </c>
       <c r="R13" t="n">
-        <v>6733625</v>
+        <v>6733607</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216548</v>
+        <v>121216554</v>
       </c>
       <c r="B14" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511619</v>
+        <v>511638</v>
       </c>
       <c r="R14" t="n">
-        <v>6733592</v>
+        <v>6733637</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2072,7 @@
         <v>121467146</v>
       </c>
       <c r="B15" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121533633</v>
+        <v>121535165</v>
       </c>
       <c r="B16" t="n">
-        <v>90727</v>
+        <v>56567</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,30 +2183,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2214,13 +2219,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511457</v>
+        <v>511406</v>
       </c>
       <c r="R16" t="n">
-        <v>6733528</v>
+        <v>6733523</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,22 +2249,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,7 +2278,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2280,17 +2289,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467155</v>
+        <v>121533633</v>
       </c>
       <c r="B17" t="n">
-        <v>91153</v>
+        <v>90733</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,25 +2308,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2326,17 +2335,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511671</v>
+        <v>511457</v>
       </c>
       <c r="R17" t="n">
-        <v>6733613</v>
+        <v>6733528</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2360,27 +2369,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Jättegranlåga</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2408,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121535165</v>
+        <v>121534290</v>
       </c>
       <c r="B18" t="n">
-        <v>56566</v>
+        <v>57355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,46 +2424,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511406</v>
+        <v>511631</v>
       </c>
       <c r="R18" t="n">
-        <v>6733523</v>
+        <v>6733617</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2486,27 +2486,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515491</v>
+        <v>121520970</v>
       </c>
       <c r="B19" t="n">
-        <v>56566</v>
+        <v>90684</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2549,45 +2549,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511409</v>
+        <v>511488</v>
       </c>
       <c r="R19" t="n">
-        <v>6733523</v>
+        <v>6733530</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2611,22 +2606,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,6 +2635,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2646,17 +2647,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467157</v>
+        <v>121515491</v>
       </c>
       <c r="B20" t="n">
-        <v>90678</v>
+        <v>56567</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,40 +2670,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511654</v>
+        <v>511409</v>
       </c>
       <c r="R20" t="n">
-        <v>6733619</v>
+        <v>6733523</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2726,22 +2732,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2750,7 +2756,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2762,17 +2767,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121529050</v>
+        <v>121467155</v>
       </c>
       <c r="B21" t="n">
-        <v>57354</v>
+        <v>91159</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2781,49 +2786,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511468</v>
+        <v>511671</v>
       </c>
       <c r="R21" t="n">
-        <v>6733517</v>
+        <v>6733613</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2847,27 +2847,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,18 +2876,9 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2904,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121534290</v>
+        <v>121467157</v>
       </c>
       <c r="B22" t="n">
-        <v>57354</v>
+        <v>90684</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2916,45 +2907,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511631</v>
+        <v>511654</v>
       </c>
       <c r="R22" t="n">
-        <v>6733617</v>
+        <v>6733619</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2978,27 +2968,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,6 +2992,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3018,17 +3004,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121520970</v>
+        <v>121529050</v>
       </c>
       <c r="B23" t="n">
-        <v>90678</v>
+        <v>57355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,30 +3023,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3068,13 +3059,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511488</v>
+        <v>511468</v>
       </c>
       <c r="R23" t="n">
-        <v>6733530</v>
+        <v>6733517</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3103,7 +3094,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3113,12 +3104,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,9 +3118,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216537</v>
+        <v>121216556</v>
       </c>
       <c r="B7" t="n">
-        <v>97058</v>
+        <v>94126</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>2383</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511618</v>
+        <v>511617</v>
       </c>
       <c r="R7" t="n">
-        <v>6733644</v>
+        <v>6733638</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216560</v>
+        <v>121216561</v>
       </c>
       <c r="B8" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511618</v>
+        <v>511610</v>
       </c>
       <c r="R8" t="n">
-        <v>6733644</v>
+        <v>6733625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216548</v>
+        <v>121216554</v>
       </c>
       <c r="B9" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511619</v>
+        <v>511638</v>
       </c>
       <c r="R9" t="n">
-        <v>6733592</v>
+        <v>6733637</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216498</v>
+        <v>121216548</v>
       </c>
       <c r="B10" t="n">
-        <v>90719</v>
+        <v>90738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511626</v>
+        <v>511619</v>
       </c>
       <c r="R10" t="n">
-        <v>6733600</v>
+        <v>6733592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216556</v>
+        <v>121216498</v>
       </c>
       <c r="B11" t="n">
-        <v>94125</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,25 +1673,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2383</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511617</v>
+        <v>511626</v>
       </c>
       <c r="R11" t="n">
-        <v>6733638</v>
+        <v>6733600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216561</v>
+        <v>121216560</v>
       </c>
       <c r="B12" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511610</v>
+        <v>511618</v>
       </c>
       <c r="R12" t="n">
-        <v>6733625</v>
+        <v>6733644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,7 +1868,7 @@
         <v>121216497</v>
       </c>
       <c r="B13" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216554</v>
+        <v>121216537</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>97059</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511638</v>
+        <v>511618</v>
       </c>
       <c r="R14" t="n">
-        <v>6733637</v>
+        <v>6733644</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2072,7 @@
         <v>121467146</v>
       </c>
       <c r="B15" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121535165</v>
+        <v>121529050</v>
       </c>
       <c r="B16" t="n">
-        <v>56567</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,35 +2183,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511406</v>
+        <v>511468</v>
       </c>
       <c r="R16" t="n">
-        <v>6733523</v>
+        <v>6733517</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,6 +2280,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2289,17 +2299,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121533633</v>
+        <v>121467157</v>
       </c>
       <c r="B17" t="n">
-        <v>90733</v>
+        <v>90685</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2308,25 +2318,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,17 +2345,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511457</v>
+        <v>511654</v>
       </c>
       <c r="R17" t="n">
-        <v>6733528</v>
+        <v>6733619</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2369,22 +2379,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121534290</v>
+        <v>121515491</v>
       </c>
       <c r="B18" t="n">
-        <v>57355</v>
+        <v>56568</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,42 +2434,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511631</v>
+        <v>511409</v>
       </c>
       <c r="R18" t="n">
-        <v>6733617</v>
+        <v>6733523</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2486,27 +2500,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,7 +2545,7 @@
         <v>121520970</v>
       </c>
       <c r="B19" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515491</v>
+        <v>121533633</v>
       </c>
       <c r="B20" t="n">
-        <v>56567</v>
+        <v>90734</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,49 +2675,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511409</v>
+        <v>511457</v>
       </c>
       <c r="R20" t="n">
-        <v>6733523</v>
+        <v>6733528</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,22 +2736,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,6 +2760,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2767,17 +2772,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467155</v>
+        <v>121534290</v>
       </c>
       <c r="B21" t="n">
-        <v>91159</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,44 +2791,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511671</v>
+        <v>511631</v>
       </c>
       <c r="R21" t="n">
-        <v>6733613</v>
+        <v>6733617</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2847,27 +2853,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Jättegranlåga</t>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,7 +2882,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2888,17 +2893,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467157</v>
+        <v>121535165</v>
       </c>
       <c r="B22" t="n">
-        <v>90684</v>
+        <v>56568</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2911,40 +2916,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511654</v>
+        <v>511406</v>
       </c>
       <c r="R22" t="n">
-        <v>6733619</v>
+        <v>6733523</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2968,22 +2978,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,7 +3007,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3004,17 +3018,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121529050</v>
+        <v>121467155</v>
       </c>
       <c r="B23" t="n">
-        <v>57355</v>
+        <v>91160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3023,49 +3037,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511468</v>
+        <v>511671</v>
       </c>
       <c r="R23" t="n">
-        <v>6733517</v>
+        <v>6733613</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3089,27 +3098,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3118,18 +3127,9 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216556</v>
+        <v>121216560</v>
       </c>
       <c r="B7" t="n">
-        <v>94126</v>
+        <v>100371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2383</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511617</v>
+        <v>511618</v>
       </c>
       <c r="R7" t="n">
-        <v>6733638</v>
+        <v>6733644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216561</v>
+        <v>121216554</v>
       </c>
       <c r="B8" t="n">
-        <v>100371</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511610</v>
+        <v>511638</v>
       </c>
       <c r="R8" t="n">
-        <v>6733625</v>
+        <v>6733637</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216554</v>
+        <v>121216498</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511638</v>
+        <v>511626</v>
       </c>
       <c r="R9" t="n">
-        <v>6733637</v>
+        <v>6733600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216498</v>
+        <v>121216497</v>
       </c>
       <c r="B11" t="n">
         <v>90720</v>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511626</v>
+        <v>511620</v>
       </c>
       <c r="R11" t="n">
-        <v>6733600</v>
+        <v>6733607</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216560</v>
+        <v>121216537</v>
       </c>
       <c r="B12" t="n">
-        <v>100371</v>
+        <v>97059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216497</v>
+        <v>121216556</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>94126</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2383</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511620</v>
+        <v>511617</v>
       </c>
       <c r="R13" t="n">
-        <v>6733607</v>
+        <v>6733638</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216537</v>
+        <v>121216561</v>
       </c>
       <c r="B14" t="n">
-        <v>97059</v>
+        <v>100371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511618</v>
+        <v>511610</v>
       </c>
       <c r="R14" t="n">
-        <v>6733644</v>
+        <v>6733625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121529050</v>
+        <v>121467155</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>91160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,49 +2183,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511468</v>
+        <v>511671</v>
       </c>
       <c r="R16" t="n">
-        <v>6733517</v>
+        <v>6733613</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2249,27 +2244,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,18 +2273,9 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2306,10 +2292,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467157</v>
+        <v>121515491</v>
       </c>
       <c r="B17" t="n">
-        <v>90685</v>
+        <v>56568</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,40 +2308,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511654</v>
+        <v>511409</v>
       </c>
       <c r="R17" t="n">
-        <v>6733619</v>
+        <v>6733523</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,22 +2370,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,7 +2394,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2415,17 +2405,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121515491</v>
+        <v>121534290</v>
       </c>
       <c r="B18" t="n">
-        <v>56568</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2434,46 +2424,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511409</v>
+        <v>511631</v>
       </c>
       <c r="R18" t="n">
-        <v>6733523</v>
+        <v>6733617</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2500,22 +2486,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,7 +2533,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121520970</v>
+        <v>121467157</v>
       </c>
       <c r="B19" t="n">
         <v>90685</v>
@@ -2581,17 +2572,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511488</v>
+        <v>511654</v>
       </c>
       <c r="R19" t="n">
-        <v>6733530</v>
+        <v>6733619</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2615,27 +2606,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,10 +2649,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121533633</v>
+        <v>121535165</v>
       </c>
       <c r="B20" t="n">
-        <v>90734</v>
+        <v>56568</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,30 +2661,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2706,13 +2697,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511457</v>
+        <v>511406</v>
       </c>
       <c r="R20" t="n">
-        <v>6733528</v>
+        <v>6733523</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,22 +2727,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,7 +2756,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2772,17 +2767,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121534290</v>
+        <v>121520970</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>90685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2791,45 +2786,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511631</v>
+        <v>511488</v>
       </c>
       <c r="R21" t="n">
-        <v>6733617</v>
+        <v>6733530</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,27 +2847,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,6 +2876,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2893,17 +2888,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121535165</v>
+        <v>121529050</v>
       </c>
       <c r="B22" t="n">
-        <v>56568</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2912,35 +2907,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2948,10 +2943,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511406</v>
+        <v>511468</v>
       </c>
       <c r="R22" t="n">
-        <v>6733523</v>
+        <v>6733517</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2978,27 +2973,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,6 +3004,16 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3018,17 +3023,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467155</v>
+        <v>121533633</v>
       </c>
       <c r="B23" t="n">
-        <v>91160</v>
+        <v>90734</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,25 +3042,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3064,17 +3069,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511671</v>
+        <v>511457</v>
       </c>
       <c r="R23" t="n">
-        <v>6733613</v>
+        <v>6733528</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3098,27 +3103,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Jättegranlåga</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467155</v>
+        <v>121529050</v>
       </c>
       <c r="B16" t="n">
-        <v>91160</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,44 +2183,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511671</v>
+        <v>511468</v>
       </c>
       <c r="R16" t="n">
-        <v>6733613</v>
+        <v>6733517</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,27 +2249,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Jättegranlåga</t>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,9 +2278,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2412,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121534290</v>
+        <v>121467155</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>91160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,45 +2438,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511631</v>
+        <v>511671</v>
       </c>
       <c r="R18" t="n">
-        <v>6733617</v>
+        <v>6733613</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2486,27 +2499,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2515,6 +2528,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2526,14 +2540,14 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467157</v>
+        <v>121520970</v>
       </c>
       <c r="B19" t="n">
         <v>90685</v>
@@ -2572,17 +2586,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511654</v>
+        <v>511488</v>
       </c>
       <c r="R19" t="n">
-        <v>6733619</v>
+        <v>6733530</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2606,22 +2620,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,10 +2668,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121535165</v>
+        <v>121467157</v>
       </c>
       <c r="B20" t="n">
-        <v>56568</v>
+        <v>90685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2665,45 +2684,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511406</v>
+        <v>511654</v>
       </c>
       <c r="R20" t="n">
-        <v>6733523</v>
+        <v>6733619</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2727,27 +2741,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,6 +2765,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2767,17 +2777,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121520970</v>
+        <v>121533633</v>
       </c>
       <c r="B21" t="n">
-        <v>90685</v>
+        <v>90734</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,25 +2796,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2817,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511488</v>
+        <v>511457</v>
       </c>
       <c r="R21" t="n">
-        <v>6733530</v>
+        <v>6733528</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2862,12 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121529050</v>
+        <v>121535165</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>56568</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2907,35 +2912,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2943,10 +2948,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511468</v>
+        <v>511406</v>
       </c>
       <c r="R22" t="n">
-        <v>6733517</v>
+        <v>6733523</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2973,27 +2978,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,16 +3009,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3023,17 +3018,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121533633</v>
+        <v>121534290</v>
       </c>
       <c r="B23" t="n">
-        <v>90734</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3046,40 +3041,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511457</v>
+        <v>511631</v>
       </c>
       <c r="R23" t="n">
-        <v>6733528</v>
+        <v>6733617</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3103,22 +3099,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,7 +3128,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121529050</v>
+        <v>121533633</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>90734</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,31 +2187,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2219,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511468</v>
+        <v>511457</v>
       </c>
       <c r="R16" t="n">
-        <v>6733517</v>
+        <v>6733528</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2254,7 +2249,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2264,12 +2259,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,18 +2268,9 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2306,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515491</v>
+        <v>121467155</v>
       </c>
       <c r="B17" t="n">
-        <v>56568</v>
+        <v>91160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,49 +2299,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511409</v>
+        <v>511671</v>
       </c>
       <c r="R17" t="n">
-        <v>6733523</v>
+        <v>6733613</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2384,22 +2360,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2408,6 +2389,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2419,17 +2401,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467155</v>
+        <v>121467157</v>
       </c>
       <c r="B18" t="n">
-        <v>91160</v>
+        <v>90685</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,25 +2420,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2469,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511671</v>
+        <v>511654</v>
       </c>
       <c r="R18" t="n">
-        <v>6733613</v>
+        <v>6733619</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2504,7 +2486,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2514,12 +2496,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Jättegranlåga</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121520970</v>
+        <v>121515491</v>
       </c>
       <c r="B19" t="n">
-        <v>90685</v>
+        <v>56568</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2563,40 +2540,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511488</v>
+        <v>511409</v>
       </c>
       <c r="R19" t="n">
-        <v>6733530</v>
+        <v>6733523</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,27 +2602,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2626,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2661,17 +2637,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467157</v>
+        <v>121529050</v>
       </c>
       <c r="B20" t="n">
-        <v>90685</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2680,44 +2656,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511654</v>
+        <v>511468</v>
       </c>
       <c r="R20" t="n">
-        <v>6733619</v>
+        <v>6733517</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,22 +2722,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,9 +2751,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2784,10 +2779,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121533633</v>
+        <v>121534290</v>
       </c>
       <c r="B21" t="n">
-        <v>90734</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2800,40 +2795,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511457</v>
+        <v>511631</v>
       </c>
       <c r="R21" t="n">
-        <v>6733528</v>
+        <v>6733617</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2857,22 +2853,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2881,7 +2882,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121534290</v>
+        <v>121520970</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>90685</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,45 +3037,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511631</v>
+        <v>511488</v>
       </c>
       <c r="R23" t="n">
-        <v>6733617</v>
+        <v>6733530</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3099,27 +3098,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,6 +3127,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>121467146</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121533633</v>
+        <v>121467155</v>
       </c>
       <c r="B16" t="n">
-        <v>90734</v>
+        <v>91168</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,25 +2183,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2210,17 +2210,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511457</v>
+        <v>511671</v>
       </c>
       <c r="R16" t="n">
-        <v>6733528</v>
+        <v>6733613</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,22 +2244,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,10 +2292,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467155</v>
+        <v>121529050</v>
       </c>
       <c r="B17" t="n">
-        <v>91160</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,44 +2304,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511671</v>
+        <v>511468</v>
       </c>
       <c r="R17" t="n">
-        <v>6733613</v>
+        <v>6733517</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2360,27 +2370,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Jättegranlåga</t>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,9 +2399,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2408,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467157</v>
+        <v>121515491</v>
       </c>
       <c r="B18" t="n">
-        <v>90685</v>
+        <v>56569</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,40 +2443,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511654</v>
+        <v>511409</v>
       </c>
       <c r="R18" t="n">
-        <v>6733619</v>
+        <v>6733523</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,22 +2505,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,7 +2529,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2517,17 +2540,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515491</v>
+        <v>121467157</v>
       </c>
       <c r="B19" t="n">
-        <v>56568</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2540,45 +2563,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511409</v>
+        <v>511654</v>
       </c>
       <c r="R19" t="n">
-        <v>6733523</v>
+        <v>6733619</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,22 +2620,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,6 +2644,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2637,17 +2656,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121529050</v>
+        <v>121535165</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>56569</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,35 +2675,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2692,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511468</v>
+        <v>511406</v>
       </c>
       <c r="R20" t="n">
-        <v>6733517</v>
+        <v>6733523</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2722,27 +2741,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,16 +2772,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2772,7 +2781,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2782,7 +2791,7 @@
         <v>121534290</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2900,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121535165</v>
+        <v>121533633</v>
       </c>
       <c r="B22" t="n">
-        <v>56568</v>
+        <v>90742</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2912,35 +2921,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2948,13 +2952,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511406</v>
+        <v>511457</v>
       </c>
       <c r="R22" t="n">
-        <v>6733523</v>
+        <v>6733528</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2978,27 +2982,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,6 +3006,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3028,7 +3028,7 @@
         <v>121520970</v>
       </c>
       <c r="B23" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121529050</v>
+        <v>121533633</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>90742</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,31 +2187,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2219,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511468</v>
+        <v>511457</v>
       </c>
       <c r="R16" t="n">
-        <v>6733517</v>
+        <v>6733528</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2254,7 +2249,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2264,12 +2259,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,18 +2268,9 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2306,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467157</v>
+        <v>121534290</v>
       </c>
       <c r="B17" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,44 +2299,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511654</v>
+        <v>511631</v>
       </c>
       <c r="R17" t="n">
-        <v>6733619</v>
+        <v>6733617</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,22 +2361,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,7 +2390,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2415,14 +2401,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121534290</v>
+        <v>121529050</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2455,21 +2441,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511631</v>
+        <v>511468</v>
       </c>
       <c r="R18" t="n">
-        <v>6733617</v>
+        <v>6733517</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2496,27 +2486,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,6 +2517,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2536,17 +2536,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121515491</v>
+        <v>121520970</v>
       </c>
       <c r="B19" t="n">
-        <v>56569</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2559,45 +2559,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511409</v>
+        <v>511488</v>
       </c>
       <c r="R19" t="n">
-        <v>6733523</v>
+        <v>6733530</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2621,22 +2616,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,6 +2645,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2656,17 +2657,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467155</v>
+        <v>121467157</v>
       </c>
       <c r="B20" t="n">
-        <v>91168</v>
+        <v>90693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,25 +2676,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2706,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511671</v>
+        <v>511654</v>
       </c>
       <c r="R20" t="n">
-        <v>6733613</v>
+        <v>6733619</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2741,7 +2742,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2751,12 +2752,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Jättegranlåga</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121520970</v>
+        <v>121515491</v>
       </c>
       <c r="B21" t="n">
-        <v>90693</v>
+        <v>56569</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2800,40 +2796,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511488</v>
+        <v>511409</v>
       </c>
       <c r="R21" t="n">
-        <v>6733530</v>
+        <v>6733523</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2857,27 +2858,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2886,7 +2882,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2898,17 +2893,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121533633</v>
+        <v>121467155</v>
       </c>
       <c r="B22" t="n">
-        <v>90742</v>
+        <v>91168</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,25 +2912,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2944,17 +2939,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511457</v>
+        <v>511671</v>
       </c>
       <c r="R22" t="n">
-        <v>6733528</v>
+        <v>6733613</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2978,22 +2973,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121533633</v>
+        <v>121520970</v>
       </c>
       <c r="B16" t="n">
-        <v>90742</v>
+        <v>90693</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,25 +2183,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511457</v>
+        <v>511488</v>
       </c>
       <c r="R16" t="n">
-        <v>6733528</v>
+        <v>6733530</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2259,7 +2259,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,10 +2292,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121534290</v>
+        <v>121467155</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>91168</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,45 +2304,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511631</v>
+        <v>511671</v>
       </c>
       <c r="R17" t="n">
-        <v>6733617</v>
+        <v>6733613</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2361,27 +2365,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,6 +2394,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2401,7 +2406,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2543,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121520970</v>
+        <v>121534290</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2555,44 +2560,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511488</v>
+        <v>511631</v>
       </c>
       <c r="R19" t="n">
-        <v>6733530</v>
+        <v>6733617</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2616,27 +2622,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,7 +2651,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2657,17 +2662,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467157</v>
+        <v>121515491</v>
       </c>
       <c r="B20" t="n">
-        <v>90693</v>
+        <v>56569</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2680,40 +2685,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511654</v>
+        <v>511409</v>
       </c>
       <c r="R20" t="n">
-        <v>6733619</v>
+        <v>6733523</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,22 +2747,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,7 +2771,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2773,17 +2782,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121515491</v>
+        <v>121467157</v>
       </c>
       <c r="B21" t="n">
-        <v>56569</v>
+        <v>90693</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,45 +2805,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511409</v>
+        <v>511654</v>
       </c>
       <c r="R21" t="n">
-        <v>6733523</v>
+        <v>6733619</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2858,22 +2862,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,6 +2886,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2893,17 +2898,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467155</v>
+        <v>121535165</v>
       </c>
       <c r="B22" t="n">
-        <v>91168</v>
+        <v>56569</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2912,44 +2917,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511671</v>
+        <v>511406</v>
       </c>
       <c r="R22" t="n">
-        <v>6733613</v>
+        <v>6733523</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,27 +2983,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Jättegranlåga</t>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3002,7 +3012,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3014,17 +3023,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121535165</v>
+        <v>121533633</v>
       </c>
       <c r="B23" t="n">
-        <v>56569</v>
+        <v>90742</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3033,35 +3042,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3069,13 +3073,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511406</v>
+        <v>511457</v>
       </c>
       <c r="R23" t="n">
-        <v>6733523</v>
+        <v>6733528</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3099,27 +3103,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,6 +3127,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121520970</v>
+        <v>121467155</v>
       </c>
       <c r="B16" t="n">
-        <v>90693</v>
+        <v>91168</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,25 +2183,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2210,17 +2210,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511488</v>
+        <v>511671</v>
       </c>
       <c r="R16" t="n">
-        <v>6733530</v>
+        <v>6733613</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,27 +2244,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2292,10 +2292,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467155</v>
+        <v>121515491</v>
       </c>
       <c r="B17" t="n">
-        <v>91168</v>
+        <v>56569</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2304,44 +2304,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511671</v>
+        <v>511409</v>
       </c>
       <c r="R17" t="n">
-        <v>6733613</v>
+        <v>6733523</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,27 +2370,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Jättegranlåga</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,7 +2394,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2406,7 +2405,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2548,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121534290</v>
+        <v>121535165</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>56569</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2560,42 +2559,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511631</v>
+        <v>511406</v>
       </c>
       <c r="R19" t="n">
-        <v>6733617</v>
+        <v>6733523</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2622,27 +2625,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121515491</v>
+        <v>121534290</v>
       </c>
       <c r="B20" t="n">
-        <v>56569</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,46 +2684,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511409</v>
+        <v>511631</v>
       </c>
       <c r="R20" t="n">
-        <v>6733523</v>
+        <v>6733617</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2747,22 +2746,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121535165</v>
+        <v>121533633</v>
       </c>
       <c r="B22" t="n">
-        <v>56569</v>
+        <v>90742</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,35 +2921,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2953,13 +2952,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511406</v>
+        <v>511457</v>
       </c>
       <c r="R22" t="n">
-        <v>6733523</v>
+        <v>6733528</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2983,27 +2982,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3012,6 +3006,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3023,17 +3018,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121533633</v>
+        <v>121520970</v>
       </c>
       <c r="B23" t="n">
-        <v>90742</v>
+        <v>90693</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,25 +3037,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3073,10 +3068,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511457</v>
+        <v>511488</v>
       </c>
       <c r="R23" t="n">
-        <v>6733528</v>
+        <v>6733530</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3108,7 +3103,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,7 +3113,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467155</v>
+        <v>121529050</v>
       </c>
       <c r="B16" t="n">
-        <v>91168</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,44 +2183,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511671</v>
+        <v>511468</v>
       </c>
       <c r="R16" t="n">
-        <v>6733613</v>
+        <v>6733517</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,27 +2249,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Jättegranlåga</t>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,9 +2278,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2412,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121529050</v>
+        <v>121520970</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,35 +2438,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2460,13 +2469,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511468</v>
+        <v>511488</v>
       </c>
       <c r="R18" t="n">
-        <v>6733517</v>
+        <v>6733530</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,7 +2504,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2505,12 +2514,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,18 +2528,9 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121535165</v>
+        <v>121533633</v>
       </c>
       <c r="B19" t="n">
-        <v>56569</v>
+        <v>90742</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2559,35 +2559,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2595,13 +2590,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511406</v>
+        <v>511457</v>
       </c>
       <c r="R19" t="n">
-        <v>6733523</v>
+        <v>6733528</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2625,27 +2620,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,6 +2644,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2665,17 +2656,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121534290</v>
+        <v>121535165</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>56569</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2684,42 +2675,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511631</v>
+        <v>511406</v>
       </c>
       <c r="R20" t="n">
-        <v>6733617</v>
+        <v>6733523</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2746,27 +2741,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,10 +2788,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467157</v>
+        <v>121534290</v>
       </c>
       <c r="B21" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2805,44 +2800,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511654</v>
+        <v>511631</v>
       </c>
       <c r="R21" t="n">
-        <v>6733619</v>
+        <v>6733617</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2866,22 +2862,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,7 +2891,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2902,17 +2902,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121533633</v>
+        <v>121467157</v>
       </c>
       <c r="B22" t="n">
-        <v>90742</v>
+        <v>90693</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2921,25 +2921,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2948,17 +2948,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511457</v>
+        <v>511654</v>
       </c>
       <c r="R22" t="n">
-        <v>6733528</v>
+        <v>6733619</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2982,22 +2982,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,10 +3025,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121520970</v>
+        <v>121467155</v>
       </c>
       <c r="B23" t="n">
-        <v>90693</v>
+        <v>91168</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,25 +3037,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3064,17 +3064,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511488</v>
+        <v>511671</v>
       </c>
       <c r="R23" t="n">
-        <v>6733530</v>
+        <v>6733613</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3098,27 +3098,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121529050</v>
+        <v>121535165</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>56569</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,35 +2183,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511468</v>
+        <v>511406</v>
       </c>
       <c r="R16" t="n">
-        <v>6733517</v>
+        <v>6733523</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,16 +2280,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2299,7 +2289,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2426,10 +2416,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121520970</v>
+        <v>121533633</v>
       </c>
       <c r="B18" t="n">
-        <v>90693</v>
+        <v>90742</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,25 +2428,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2469,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511488</v>
+        <v>511457</v>
       </c>
       <c r="R18" t="n">
-        <v>6733530</v>
+        <v>6733528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,7 +2494,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2514,12 +2504,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,10 +2532,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121533633</v>
+        <v>121534290</v>
       </c>
       <c r="B19" t="n">
-        <v>90742</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2563,40 +2548,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511457</v>
+        <v>511631</v>
       </c>
       <c r="R19" t="n">
-        <v>6733528</v>
+        <v>6733617</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,22 +2606,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,7 +2635,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2656,17 +2646,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121535165</v>
+        <v>121467157</v>
       </c>
       <c r="B20" t="n">
-        <v>56569</v>
+        <v>90693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2679,45 +2669,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511406</v>
+        <v>511654</v>
       </c>
       <c r="R20" t="n">
-        <v>6733523</v>
+        <v>6733619</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,27 +2726,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,6 +2750,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2781,17 +2762,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121534290</v>
+        <v>121520970</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2800,45 +2781,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511631</v>
+        <v>511488</v>
       </c>
       <c r="R21" t="n">
-        <v>6733617</v>
+        <v>6733530</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2862,27 +2842,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,6 +2871,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2902,17 +2883,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467157</v>
+        <v>121529050</v>
       </c>
       <c r="B22" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2921,44 +2902,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511654</v>
+        <v>511468</v>
       </c>
       <c r="R22" t="n">
-        <v>6733619</v>
+        <v>6733517</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2982,22 +2968,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,9 +2997,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>121526891</v>
       </c>
       <c r="B24" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>121526891</v>
       </c>
       <c r="B24" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2535,7 +2535,7 @@
         <v>121534290</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>121526891</v>
       </c>
       <c r="B24" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>121526891</v>
       </c>
       <c r="B24" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>121526891</v>
       </c>
       <c r="B24" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2174,12 +2174,7 @@
         <v>121535165</v>
       </c>
       <c r="B16" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,7 +2264,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning.</t>
+          <t>Färska fotspår i nattgammal snö. AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3255,6 +3255,245 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126258868</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stor Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>511446</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6733516</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126258881</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stor Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>511466</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6733539</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Jag vet inte exakt var i Moberg spillkråkorna bor men att de har permanenta revir kan man vara säker på. De hörs och de lämnar spår efter sig.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2174,7 +2174,7 @@
         <v>121535165</v>
       </c>
       <c r="B16" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>126258868</v>
       </c>
       <c r="B25" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>126258881</v>
       </c>
       <c r="B26" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -2174,7 +2174,7 @@
         <v>121535165</v>
       </c>
       <c r="B16" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>126258868</v>
       </c>
       <c r="B25" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>126258881</v>
       </c>
       <c r="B26" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3499,7 +3499,7 @@
         <v>127085277</v>
       </c>
       <c r="B27" t="n">
-        <v>91832</v>
+        <v>91906</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127085482</v>
       </c>
       <c r="B29" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127085332</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127085487</v>
       </c>
       <c r="B31" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127085485</v>
       </c>
       <c r="B32" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127085484</v>
       </c>
       <c r="B33" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127085483</v>
       </c>
       <c r="B34" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127085123</v>
       </c>
       <c r="B35" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>127015415</v>
       </c>
       <c r="B36" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127015504</v>
       </c>
       <c r="B38" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3499,7 +3499,7 @@
         <v>127085277</v>
       </c>
       <c r="B27" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127085482</v>
       </c>
       <c r="B29" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127085332</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127085487</v>
       </c>
       <c r="B31" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127085485</v>
       </c>
       <c r="B32" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127085484</v>
       </c>
       <c r="B33" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127085483</v>
       </c>
       <c r="B34" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127085123</v>
       </c>
       <c r="B35" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>127015415</v>
       </c>
       <c r="B36" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127015504</v>
       </c>
       <c r="B38" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3499,7 +3499,7 @@
         <v>127085277</v>
       </c>
       <c r="B27" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127085482</v>
       </c>
       <c r="B29" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127085487</v>
       </c>
       <c r="B31" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127085485</v>
       </c>
       <c r="B32" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127085484</v>
       </c>
       <c r="B33" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127085483</v>
       </c>
       <c r="B34" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127085123</v>
       </c>
       <c r="B35" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>127015415</v>
       </c>
       <c r="B36" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127015504</v>
       </c>
       <c r="B38" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3499,7 +3499,7 @@
         <v>127085277</v>
       </c>
       <c r="B27" t="n">
-        <v>91913</v>
+        <v>91917</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>127085143</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127085482</v>
       </c>
       <c r="B29" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127085332</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127085487</v>
       </c>
       <c r="B31" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127085485</v>
       </c>
       <c r="B32" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127085484</v>
       </c>
       <c r="B33" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127085483</v>
       </c>
       <c r="B34" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127085123</v>
       </c>
       <c r="B35" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>127015415</v>
       </c>
       <c r="B36" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>127014469</v>
       </c>
       <c r="B37" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127015504</v>
       </c>
       <c r="B38" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3703,7 +3703,7 @@
         <v>127085482</v>
       </c>
       <c r="B29" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127085487</v>
       </c>
       <c r="B31" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127085485</v>
       </c>
       <c r="B32" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127085484</v>
       </c>
       <c r="B33" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127085483</v>
       </c>
       <c r="B34" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3499,7 +3499,7 @@
         <v>127085277</v>
       </c>
       <c r="B27" t="n">
-        <v>91917</v>
+        <v>91919</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>127085143</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127085482</v>
       </c>
       <c r="B29" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127085332</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127085487</v>
       </c>
       <c r="B31" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127085485</v>
       </c>
       <c r="B32" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127085484</v>
       </c>
       <c r="B33" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127085483</v>
       </c>
       <c r="B34" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127085123</v>
       </c>
       <c r="B35" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>127015415</v>
       </c>
       <c r="B36" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>127014469</v>
       </c>
       <c r="B37" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127015504</v>
       </c>
       <c r="B38" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4698,6 +4698,297 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127784892</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91739</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Grim Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>511479</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6733529</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127784885</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80152</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grim Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>511496</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6733540</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127784883</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92029</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Grim Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>511616</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6733596</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3499,7 +3499,7 @@
         <v>127085277</v>
       </c>
       <c r="B27" t="n">
-        <v>91919</v>
+        <v>91925</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127085482</v>
       </c>
       <c r="B29" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127085487</v>
       </c>
       <c r="B31" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127085485</v>
       </c>
       <c r="B32" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127085484</v>
       </c>
       <c r="B33" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127085483</v>
       </c>
       <c r="B34" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127085123</v>
       </c>
       <c r="B35" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>127015415</v>
       </c>
       <c r="B36" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127015504</v>
       </c>
       <c r="B38" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>127784892</v>
       </c>
       <c r="B39" t="n">
-        <v>91739</v>
+        <v>91745</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>127784883</v>
       </c>
       <c r="B41" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3499,7 +3499,7 @@
         <v>127085277</v>
       </c>
       <c r="B27" t="n">
-        <v>91925</v>
+        <v>91928</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>127085143</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127085482</v>
       </c>
       <c r="B29" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127085332</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127085487</v>
       </c>
       <c r="B31" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127085485</v>
       </c>
       <c r="B32" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127085484</v>
       </c>
       <c r="B33" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127085483</v>
       </c>
       <c r="B34" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127085123</v>
       </c>
       <c r="B35" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>127015415</v>
       </c>
       <c r="B36" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>127014469</v>
       </c>
       <c r="B37" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127015504</v>
       </c>
       <c r="B38" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>127784892</v>
       </c>
       <c r="B39" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>127784885</v>
       </c>
       <c r="B40" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>127784883</v>
       </c>
       <c r="B41" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -4382,7 +4382,7 @@
         <v>127015415</v>
       </c>
       <c r="B36" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>127014469</v>
       </c>
       <c r="B37" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127015504</v>
       </c>
       <c r="B38" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>127784892</v>
       </c>
       <c r="B39" t="n">
-        <v>91748</v>
+        <v>91756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>127784885</v>
       </c>
       <c r="B40" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>127784883</v>
       </c>
       <c r="B41" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>127784892</v>
       </c>
       <c r="B39" t="n">
-        <v>91756</v>
+        <v>91757</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>127784883</v>
       </c>
       <c r="B41" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>127784892</v>
       </c>
       <c r="B39" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>127784883</v>
       </c>
       <c r="B41" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>127784892</v>
       </c>
       <c r="B39" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>127784883</v>
       </c>
       <c r="B41" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>127784892</v>
       </c>
       <c r="B39" t="n">
-        <v>91759</v>
+        <v>91767</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>127784885</v>
       </c>
       <c r="B40" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>127784883</v>
       </c>
       <c r="B41" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>127784892</v>
       </c>
       <c r="B39" t="n">
-        <v>91767</v>
+        <v>91859</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>127784885</v>
       </c>
       <c r="B40" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>127784883</v>
       </c>
       <c r="B41" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4989,6 +4989,237 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129174190</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stor Moberg Norra , Stor Moberg Norra , Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>511456</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6733513</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Troligen ett bohål, rester av mossa.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129174357</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stor Moberg Norra , Stor Moberg Norra , Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>511456</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6733513</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -4994,7 +4994,7 @@
         <v>129174190</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -4994,7 +4994,7 @@
         <v>129174190</v>
       </c>
       <c r="B42" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -4994,7 +4994,7 @@
         <v>129174190</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>129174357</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -3499,7 +3499,7 @@
         <v>127085277</v>
       </c>
       <c r="B27" t="n">
-        <v>91928</v>
+        <v>91906</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>127085143</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127085482</v>
       </c>
       <c r="B29" t="n">
-        <v>100641</v>
+        <v>100618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127085332</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127085487</v>
       </c>
       <c r="B31" t="n">
-        <v>100641</v>
+        <v>100618</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127085485</v>
       </c>
       <c r="B32" t="n">
-        <v>100641</v>
+        <v>100618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127085484</v>
       </c>
       <c r="B33" t="n">
-        <v>100641</v>
+        <v>100618</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127085483</v>
       </c>
       <c r="B34" t="n">
-        <v>100641</v>
+        <v>100618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127085123</v>
       </c>
       <c r="B35" t="n">
-        <v>91341</v>
+        <v>91319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>127015415</v>
       </c>
       <c r="B36" t="n">
-        <v>91349</v>
+        <v>91319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>127014469</v>
       </c>
       <c r="B37" t="n">
-        <v>58042</v>
+        <v>58027</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>127015504</v>
       </c>
       <c r="B38" t="n">
-        <v>97344</v>
+        <v>97314</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>106215906</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511406.0020477105</v>
+        <v>511406</v>
       </c>
       <c r="R2" t="n">
-        <v>6733516.38421111</v>
+        <v>6733516</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -796,54 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112043031</v>
+        <v>127085277</v>
       </c>
       <c r="B3" t="n">
-        <v>90481</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-Moberg (Stor-Moberg), Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511625</v>
+        <v>511674</v>
       </c>
       <c r="R3" t="n">
-        <v>6733616</v>
+        <v>6733625</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,66 +876,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112043158</v>
+        <v>121216497</v>
       </c>
       <c r="B4" t="n">
-        <v>95702</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Moberg (Stor-Moberg), Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511628</v>
+        <v>511620</v>
       </c>
       <c r="R4" t="n">
-        <v>6733623</v>
+        <v>6733607</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,27 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Finns fläckvis i området</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,66 +973,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112042940</v>
+        <v>121216498</v>
       </c>
       <c r="B5" t="n">
-        <v>98989</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Moberg (Stor-Moberg), Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511611</v>
+        <v>511626</v>
       </c>
       <c r="R5" t="n">
-        <v>6733626</v>
+        <v>6733600</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,27 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fullt med blåsippsblad på denna sidan bäcken</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,27 +1070,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112044333</v>
+        <v>121467146</v>
       </c>
       <c r="B6" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,38 +1093,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stor Mpmerg, Kilen-Stor, Moberg, Leksand, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>511614</v>
       </c>
       <c r="R6" t="n">
-        <v>6733640</v>
+        <v>6733603</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,17 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 2</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,62 +1167,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216560</v>
+        <v>121510962</v>
       </c>
       <c r="B7" t="n">
-        <v>100371</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511618</v>
+        <v>511610</v>
       </c>
       <c r="R7" t="n">
-        <v>6733644</v>
+        <v>6733676</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,12 +1247,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,33 +1271,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216554</v>
+        <v>121514534</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,34 +1301,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511638</v>
+        <v>511706</v>
       </c>
       <c r="R8" t="n">
-        <v>6733637</v>
+        <v>6733638</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,12 +1358,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,33 +1372,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216498</v>
+        <v>121526891</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,16 +1420,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511626</v>
+        <v>511459</v>
       </c>
       <c r="R9" t="n">
-        <v>6733600</v>
+        <v>6733523</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,12 +1459,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,33 +1483,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216548</v>
+        <v>127015415</v>
       </c>
       <c r="B10" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,34 +1513,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Stor Moberg Norra, Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511619</v>
+        <v>511454</v>
       </c>
       <c r="R10" t="n">
-        <v>6733592</v>
+        <v>6733522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,12 +1567,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,27 +1597,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216497</v>
+        <v>127085123</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,14 +1640,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511620</v>
+        <v>511628</v>
       </c>
       <c r="R11" t="n">
-        <v>6733607</v>
+        <v>6733598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,12 +1674,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,50 +1706,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216537</v>
+        <v>127784881</v>
       </c>
       <c r="B12" t="n">
-        <v>97059</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511618</v>
+        <v>511565</v>
       </c>
       <c r="R12" t="n">
-        <v>6733644</v>
+        <v>6733535</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,12 +1771,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,50 +1803,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216556</v>
+        <v>129174357</v>
       </c>
       <c r="B13" t="n">
-        <v>94126</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2383</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Stor Moberg Norra , Stor Moberg Norra , Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511617</v>
+        <v>511456</v>
       </c>
       <c r="R13" t="n">
-        <v>6733638</v>
+        <v>6733513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,12 +1871,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,68 +1895,67 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216561</v>
+        <v>121533633</v>
       </c>
       <c r="B14" t="n">
-        <v>100371</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511610</v>
+        <v>511457</v>
       </c>
       <c r="R14" t="n">
-        <v>6733625</v>
+        <v>6733528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,12 +1982,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,71 +2006,67 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467146</v>
+        <v>127784895</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511614</v>
+        <v>511533</v>
       </c>
       <c r="R15" t="n">
-        <v>6733603</v>
+        <v>6733530</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,12 +2090,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,68 +2110,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121535165</v>
+        <v>111966368</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511406</v>
+        <v>511648</v>
       </c>
       <c r="R16" t="n">
-        <v>6733523</v>
+        <v>6733569</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,27 +2188,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska fotspår i nattgammal snö. AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2284,68 +2223,58 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515491</v>
+        <v>121467155</v>
       </c>
       <c r="B17" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511409</v>
+        <v>511671</v>
       </c>
       <c r="R17" t="n">
-        <v>6733523</v>
+        <v>6733613</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2369,22 +2298,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Jättegranlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2393,6 +2327,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2404,22 +2339,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121533633</v>
+        <v>121467159</v>
       </c>
       <c r="B18" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,21 +2357,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2450,17 +2380,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511457</v>
+        <v>511544</v>
       </c>
       <c r="R18" t="n">
-        <v>6733528</v>
+        <v>6733530</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2484,22 +2414,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,15 +2457,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121534290</v>
+        <v>121510903</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2543,41 +2468,48 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor Moberg , Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511631</v>
+        <v>511610</v>
       </c>
       <c r="R19" t="n">
-        <v>6733617</v>
+        <v>6733676</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2601,27 +2533,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
+          <t>Uppskattat antal dm² eftersom jag inte mätte bredden. Det var ett större område ca 180 cm långt och ett mindre ca 80 cm långt + fläckvis.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2630,6 +2562,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2648,15 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467157</v>
+        <v>121216556</v>
       </c>
       <c r="B20" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2664,40 +2592,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>2383</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511654</v>
+        <v>511617</v>
       </c>
       <c r="R20" t="n">
-        <v>6733619</v>
+        <v>6733638</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2721,22 +2646,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,34 +2660,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121520970</v>
+        <v>127784883</v>
       </c>
       <c r="B21" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,37 +2689,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511488</v>
+        <v>511616</v>
       </c>
       <c r="R21" t="n">
-        <v>6733530</v>
+        <v>6733596</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,27 +2743,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2866,77 +2757,66 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121529050</v>
+        <v>127114129</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511468</v>
+        <v>511346</v>
       </c>
       <c r="R22" t="n">
-        <v>6733517</v>
+        <v>6733496</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2963,27 +2843,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>En bit ifrån denna gamla tall hade jag hört en hackspett födosöka med mjuka hack men när jag smög närmare flög den iväg.  Det var definitivt inte en Större hackspett som födosökte. Den 8/12 i hörde jag samma mjuka hackande och då såg min make att det var tretåig hackspett.</t>
+          <t>Jag hittade bilden idag bland alla bilder jag har från hösten 2022 på Mobergkammen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,18 +2872,9 @@
       <c r="AE22" t="b">
         <v>1</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Kontinuitetsbarrblandskog med övervägande gran. Väldigt många granar med flakhack (slanthack). En hel del lövträd. Väldigt mycket död ved både liggande, stående och lutande och i olika åldrar. En stor andel grova granar, och en del riktigt gamla tallar. Flera öppna källor, rörligt markvatten.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3020,56 +2891,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467155</v>
+        <v>112043031</v>
       </c>
       <c r="B23" t="n">
-        <v>91168</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511671</v>
+        <v>511625</v>
       </c>
       <c r="R23" t="n">
-        <v>6733613</v>
+        <v>6733616</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3093,27 +2957,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Jättegranlåga</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,7 +2981,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3141,37 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121526891</v>
+        <v>121467157</v>
       </c>
       <c r="B24" t="n">
-        <v>90966</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3180,17 +3033,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511459</v>
+        <v>511654</v>
       </c>
       <c r="R24" t="n">
-        <v>6733523</v>
+        <v>6733619</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,22 +3067,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,53 +3110,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126258868</v>
+        <v>121520970</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor Moberg, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511446</v>
+        <v>511488</v>
       </c>
       <c r="R25" t="n">
-        <v>6733516</v>
+        <v>6733530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3330,22 +3178,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,6 +3207,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3372,57 +3226,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126258881</v>
+        <v>121526747</v>
       </c>
       <c r="B26" t="n">
-        <v>57654</v>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor Moberg, Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511466</v>
+        <v>511414</v>
       </c>
       <c r="R26" t="n">
-        <v>6733539</v>
+        <v>6733490</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3449,27 +3294,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Jag vet inte exakt var i Moberg spillkråkorna bor men att de har permanenta revir kan man vara säker på. De hörs och de lämnar spår efter sig.</t>
+          <t>Typisk art i 9010 Taiga (Boreal region (BOR))</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3478,6 +3323,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3496,45 +3342,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127085277</v>
+        <v>127784874</v>
       </c>
       <c r="B27" t="n">
-        <v>91928</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1179</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511674</v>
+        <v>511545</v>
       </c>
       <c r="R27" t="n">
-        <v>6733625</v>
+        <v>6733530</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,12 +3407,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3593,50 +3439,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127085143</v>
+        <v>127784875</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511615</v>
+        <v>511538</v>
       </c>
       <c r="R28" t="n">
-        <v>6733590</v>
+        <v>6733530</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3663,24 +3504,19 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Talrika troliga spår efter födosök</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3700,10 +3536,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127085482</v>
+        <v>127784876</v>
       </c>
       <c r="B29" t="n">
-        <v>100641</v>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,34 +3547,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511617</v>
+        <v>511485</v>
       </c>
       <c r="R29" t="n">
-        <v>6733663</v>
+        <v>6733512</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3765,12 +3601,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,14 +3633,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127085332</v>
+        <v>121216554</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3828,14 +3664,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511680</v>
+        <v>511638</v>
       </c>
       <c r="R30" t="n">
-        <v>6733612</v>
+        <v>6733637</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3862,12 +3698,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3894,45 +3730,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127085487</v>
+        <v>127085318</v>
       </c>
       <c r="B31" t="n">
-        <v>100641</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511611</v>
+        <v>511695</v>
       </c>
       <c r="R31" t="n">
-        <v>6733621</v>
+        <v>6733590</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3965,6 +3801,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På minst 250 år gammal tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3991,45 +3832,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127085485</v>
+        <v>127085329</v>
       </c>
       <c r="B32" t="n">
-        <v>100641</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511612</v>
+        <v>511692</v>
       </c>
       <c r="R32" t="n">
-        <v>6733632</v>
+        <v>6733588</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4088,45 +3929,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127085484</v>
+        <v>127085330</v>
       </c>
       <c r="B33" t="n">
-        <v>100641</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511620</v>
+        <v>511679</v>
       </c>
       <c r="R33" t="n">
-        <v>6733643</v>
+        <v>6733601</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,45 +4026,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127085483</v>
+        <v>127085332</v>
       </c>
       <c r="B34" t="n">
-        <v>100641</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511619</v>
+        <v>511680</v>
       </c>
       <c r="R34" t="n">
-        <v>6733653</v>
+        <v>6733612</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4282,45 +4123,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127085123</v>
+        <v>127784885</v>
       </c>
       <c r="B35" t="n">
-        <v>91341</v>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511628</v>
+        <v>511496</v>
       </c>
       <c r="R35" t="n">
-        <v>6733598</v>
+        <v>6733540</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4347,12 +4188,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4379,48 +4225,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127015415</v>
+        <v>106212758</v>
       </c>
       <c r="B36" t="n">
-        <v>91349</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Stor Moberg Norra, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511454</v>
+        <v>511346</v>
       </c>
       <c r="R36" t="n">
-        <v>6733522</v>
+        <v>6733488</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4444,29 +4294,34 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Har denna asp skadats av människorhand för länge sedan? Har en spillkråka sökt föda i närtid?</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4479,17 +4334,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127014469</v>
+        <v>126258868</v>
       </c>
       <c r="B37" t="n">
-        <v>58042</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4497,16 +4352,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4515,16 +4370,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511665</v>
+        <v>511446</v>
       </c>
       <c r="R37" t="n">
-        <v>6733624</v>
+        <v>6733516</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4551,22 +4414,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4593,10 +4456,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127015504</v>
+        <v>126258881</v>
       </c>
       <c r="B38" t="n">
-        <v>97344</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4604,34 +4467,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra, Stor Moberg Norra, Dlr</t>
+          <t>Stor Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511435</v>
+        <v>511466</v>
       </c>
       <c r="R38" t="n">
-        <v>6733526</v>
+        <v>6733539</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4658,22 +4533,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Jag vet inte exakt var i Moberg spillkråkorna bor men att de har permanenta revir kan man vara säker på. De hörs och de lämnar spår efter sig.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4700,40 +4580,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127784892</v>
+        <v>127015008</v>
       </c>
       <c r="B39" t="n">
-        <v>91859</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grim Moberg, Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511479</v>
+        <v>511699</v>
       </c>
       <c r="R39" t="n">
-        <v>6733529</v>
+        <v>6733622</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4760,12 +4645,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4780,22 +4675,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127784885</v>
+        <v>129174190</v>
       </c>
       <c r="B40" t="n">
-        <v>80217</v>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4803,34 +4698,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grim Moberg, Dlr</t>
+          <t>Stor Moberg Norra , Stor Moberg Norra , Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511496</v>
+        <v>511456</v>
       </c>
       <c r="R40" t="n">
-        <v>6733540</v>
+        <v>6733513</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4857,17 +4760,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Troligen ett bohål, rester av mossa.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4882,22 +4795,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127784883</v>
+        <v>127014855</v>
       </c>
       <c r="B41" t="n">
-        <v>92149</v>
+        <v>57258</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,34 +4818,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>100065</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grim Moberg, Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511616</v>
+        <v>511699</v>
       </c>
       <c r="R41" t="n">
-        <v>6733596</v>
+        <v>6733622</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4959,12 +4872,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4979,22 +4902,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174190</v>
+        <v>121527373</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5002,16 +4925,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5022,25 +4945,21 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra , Stor Moberg Norra , Dlr</t>
+          <t>Stor Moberg Norra, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511456</v>
+        <v>511517</v>
       </c>
       <c r="R42" t="n">
-        <v>6733513</v>
+        <v>6733535</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5064,37 +4983,47 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Troligen ett bohål, rester av mossa.</t>
+          <t>Det finns fynd av hack i närheten och man har sett tretåiga hackspettar i Mobergkammen (en längre urbergskedja).</t>
         </is>
       </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog, gammal fäbodskog med stort inslag av lövträd (sälg, björk, rönn och ev något mera).  Barrblandskog, med gamla tallar! Mycket död ved. Flera källor i området och rörligt markvatten. AVVERKNINGSANMÄLD SKOG!</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5104,17 +5033,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129174357</v>
+        <v>121534290</v>
       </c>
       <c r="B43" t="n">
-        <v>91581</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5122,40 +5051,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor Moberg Norra , Stor Moberg Norra , Dlr</t>
+          <t>Stor Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511456</v>
+        <v>511631</v>
       </c>
       <c r="R43" t="n">
-        <v>6733513</v>
+        <v>6733617</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5179,22 +5109,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Flakhack/slanthack på många granar i den vackra bäckravinen. Många granar kring bäcken har styltor, dvs rötterna gör att granen kommer upp en bit från marken.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5203,7 +5138,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5219,6 +5153,2994 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127085143</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Grim-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>511615</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6733590</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Talrika troliga spår efter födosök</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121515491</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>511409</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6733523</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121535165</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stor Moberg Norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>511406</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6733523</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska fotspår i nattgammal snö. AVVERKNINGSANMÄLD KONTINUITETSBARRSKOG. Övervägande gran men även mycket gamla tallar, väldigt mycket död ved (stående, lutande, liggande, vindfällen, toppbrott etc) luckig med lövinblandning. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127085165</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>511678</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6733602</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127085166</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Grim-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>511354</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6733445</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>106212374</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>511343</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6733476</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-01-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127014946</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57774</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>511699</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6733622</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127014469</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>511665</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6733624</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127014933</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>511699</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6733622</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>112043158</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>511628</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6733623</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Finns fläckvis i området</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121216537</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>511618</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6733644</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127015504</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stor Moberg Norra, Stor Moberg Norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>511435</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6733526</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127085229</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Grim-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>511627</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6733567</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>111966750</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>511474</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6733504</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>112042940</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>511611</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6733626</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fullt med blåsippsblad på denna sidan bäcken</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>121216560</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>511618</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6733644</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>121216561</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>511610</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6733625</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121511236</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>511611</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6733683</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Det råkade bara komma fram några blåsippsblad och jag vet inte hur stort blåsippsområdet är under snön.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127085478</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>511619</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6733685</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127085480</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>511621</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6733687</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127085481</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>511623</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6733673</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127085482</v>
+      </c>
+      <c r="B65" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stor-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>511617</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6733663</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127085483</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Grim-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>511619</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6733653</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127085484</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Grim-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>511620</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6733643</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127085485</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Grim-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>511612</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6733632</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127085487</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Grim-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>511611</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6733621</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127784903</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Grim Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>511584</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6733660</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127784904</v>
+      </c>
+      <c r="B71" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Grim Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>511590</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6733644</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127784892</v>
+      </c>
+      <c r="B72" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Grim Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>511479</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6733529</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59850-2022 artfynd.xlsx
+++ b/artfynd/A 59850-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106215906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085277</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216497</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216498</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467146</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121510962</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121514534</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,6 +1539,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121526891</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127015415</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1703,6 +1753,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085123</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1800,6 +1855,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784881</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1911,6 +1971,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174357</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2022,6 +2087,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121533633</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784895</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2227,6 +2302,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966368</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2343,6 +2423,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467155</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2454,6 +2539,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467159</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121510903</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2675,6 +2770,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216556</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784883</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2888,6 +2993,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127114129</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2996,6 +3106,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043031</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3107,6 +3222,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467157</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3223,6 +3343,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121520970</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3339,6 +3464,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121526747</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3436,6 +3566,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784874</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3533,6 +3668,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784875</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3630,6 +3770,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784876</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3727,6 +3872,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216554</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3829,6 +3979,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085318</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3926,6 +4081,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085329</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4023,6 +4183,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085330</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4120,6 +4285,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085332</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4222,6 +4392,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784885</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4338,6 +4513,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106212758</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4453,6 +4633,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258868</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4577,6 +4762,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258881</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4684,6 +4874,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127015008</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4804,6 +4999,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174190</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4911,6 +5111,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127014855</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5037,6 +5242,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527373</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5153,6 +5363,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121534290</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5260,6 +5475,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085143</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5375,6 +5595,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121515491</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5495,6 +5720,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121535165</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5597,6 +5827,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085165</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5699,6 +5934,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085166</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5807,6 +6047,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106212374</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5914,6 +6159,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127014946</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6021,6 +6271,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127014469</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6128,6 +6383,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127014933</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6241,6 +6501,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043158</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6338,6 +6603,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216537</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6445,6 +6715,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127015504</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6542,6 +6817,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085229</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6650,6 +6930,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966750</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6763,6 +7048,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112042940</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6860,6 +7150,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216560</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6957,6 +7252,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216561</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7074,6 +7374,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121511236</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7171,6 +7476,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085478</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7268,6 +7578,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085480</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7365,6 +7680,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085481</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7462,6 +7782,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085482</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7559,6 +7884,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085483</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7656,6 +7986,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085484</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7753,6 +8088,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085485</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7850,6 +8190,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085487</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7947,6 +8292,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784903</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8044,6 +8394,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784904</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8141,8 +8496,86 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784892</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>